--- a/data/trans_bre/P1419-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P1419-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,89</t>
+          <t>0,87</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>106,91%</t>
+          <t>94,7%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,01; 12,44</t>
+          <t>3,21; 12,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,89; 8,36</t>
+          <t>2,0; 8,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,54; 9,25</t>
+          <t>2,55; 9,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 2,24</t>
+          <t>-0,39; 2,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>47,67; 538,32</t>
+          <t>51,52; 513,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,06; —</t>
+          <t>64,82; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,8; 2319,16</t>
+          <t>39,36; 2311,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-53,15; 739,95</t>
+          <t>-38,9; 917,52</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,34</t>
+          <t>7,26</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>253,1%</t>
+          <t>248,85%</t>
         </is>
       </c>
     </row>
@@ -760,32 +760,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,38; 9,85</t>
+          <t>3,38; 10,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,2; 7,22</t>
+          <t>2,11; 7,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,74; 4,13</t>
+          <t>0,71; 3,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,57; 9,89</t>
+          <t>4,81; 10,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>58,93; 398,47</t>
+          <t>53,96; 417,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>63,88; 1039,25</t>
+          <t>54,13; 1045,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>99,62; 529,57</t>
+          <t>107,06; 547,75</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,06</t>
+          <t>4,39</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>103,23%</t>
+          <t>112,45%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,47; 7,98</t>
+          <t>2,27; 8,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,75; 5,51</t>
+          <t>0,81; 5,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,84; 15,05</t>
+          <t>6,77; 14,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,97; 6,8</t>
+          <t>0,84; 6,99</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>62,29; 2141,08</t>
+          <t>83,86; 2068,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 1318,88</t>
+          <t>9,16; 1280,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>228,44; 3174,37</t>
+          <t>224,5; 2238,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,15; 274,44</t>
+          <t>10,81; 264,35</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,27</t>
+          <t>4,31</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>158,1%</t>
+          <t>189,77%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,13; 14,06</t>
+          <t>7,03; 14,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,57; 14,95</t>
+          <t>7,32; 15,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,12; 9,74</t>
+          <t>3,05; 9,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,06; 5,69</t>
+          <t>1,3; 6,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>215,79; 1992,78</t>
+          <t>207,74; 1982,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>228,09; 4716,07</t>
+          <t>243,4; 4245,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,38; 1272,42</t>
+          <t>90,1; 1459,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 540,03</t>
+          <t>23,89; 657,95</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14,19</t>
+          <t>13,17</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>218,84%</t>
+          <t>209,43%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,05; 10,0</t>
+          <t>1,99; 10,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,95; 19,8</t>
+          <t>9,15; 20,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 4,21</t>
+          <t>-1,85; 4,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,66; 18,52</t>
+          <t>8,83; 17,3</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,44; 1857,87</t>
+          <t>42,31; 2212,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>176,9; 1784,8</t>
+          <t>134,49; 1787,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-57,21; 675,96</t>
+          <t>-69,18; 739,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>103,3; 447,27</t>
+          <t>98,52; 375,32</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10,68</t>
+          <t>10,55</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>274,31%</t>
+          <t>265,63%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,14; 14,67</t>
+          <t>6,36; 14,66</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,76; 10,54</t>
+          <t>3,65; 10,54</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,15; 8,0</t>
+          <t>1,27; 7,65</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,14; 14,17</t>
+          <t>7,17; 14,17</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>142,23; 2552,7</t>
+          <t>141,57; 2734,13</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>114,57; 2493,64</t>
+          <t>136,78; 2516,95</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,64; 2169,42</t>
+          <t>14,45; 1882,19</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>130,43; 567,81</t>
+          <t>126,62; 536,73</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8,28</t>
+          <t>13,32</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>158,73%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,21; 8,92</t>
+          <t>4,47; 9,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,55; 11,81</t>
+          <t>6,76; 11,74</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,23; 5,73</t>
+          <t>1,52; 5,82</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 14,69</t>
+          <t>9,95; 16,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>172,24; 1022,19</t>
+          <t>170,98; 1032,28</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>317,71; 3060,57</t>
+          <t>313,07; 3413,51</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,76; 455,55</t>
+          <t>43,52; 388,26</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-7,85; 186,57</t>
+          <t>98,05; 237,93</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3,48</t>
+          <t>3,07</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>300,21%</t>
+          <t>203,24%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,08; 11,98</t>
+          <t>6,24; 12,38</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,58; 8,94</t>
+          <t>4,79; 8,66</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,12; 7,34</t>
+          <t>2,99; 7,14</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,96; 5,06</t>
+          <t>1,74; 4,6</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>83,65; 258,17</t>
+          <t>88,44; 266,94</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>264,68; 1510,01</t>
+          <t>246,15; 1580,31</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>97,29; 549,44</t>
+          <t>99,17; 650,73</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>93,12; 869,26</t>
+          <t>74,71; 487,76</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6,49</t>
+          <t>7,06</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>184,25%</t>
+          <t>184,27%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,67; 9,01</t>
+          <t>6,55; 9,06</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,28; 8,35</t>
+          <t>6,23; 8,22</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,69; 5,66</t>
+          <t>3,68; 5,59</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,63; 7,74</t>
+          <t>6,07; 8,08</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>192,27; 355,19</t>
+          <t>181,26; 357,87</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>415,34; 925,64</t>
+          <t>411,1; 927,25</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>193,28; 453,77</t>
+          <t>197,03; 452,1</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>125,75; 266,53</t>
+          <t>140,01; 235,56</t>
         </is>
       </c>
     </row>
